--- a/test_data/RegBriefings/RegBriefings Archive/RegBriefings Archive_Test_Cases.xlsx
+++ b/test_data/RegBriefings/RegBriefings Archive/RegBriefings Archive_Test_Cases.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Clicking the monthly card correctly navigated to https://regplus.reganalytics.com/regbrief/pastBriefingDetails?type=WtaBriefing&amp;month=December&amp;year=2025.</t>
+          <t>Clicking the monthly card correctly navigated to https://regplusrc.reganalytics.com/regbrief/pastBriefingDetails?type=WtaBriefing&amp;month=December&amp;year=2025.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
